--- a/2026IAD215_Jennel Kate Fortin(1)_test_output.xlsx
+++ b/2026IAD215_Jennel Kate Fortin(1)_test_output.xlsx
@@ -160,7 +160,7 @@
     <t>She was not able to process her latest replenishment earlier due to busy schedule.</t>
   </si>
   <si>
-    <t>Ms. Jennel Kate Fortin should explain further regarding this shortage.</t>
+    <t>Should explain further regarding this shortage.</t>
   </si>
   <si>
     <t>Promptly prepare the PCV after completing the fund transaction.</t>
@@ -187,7 +187,7 @@
     <t>First Time</t>
   </si>
   <si>
-    <t>Ms.</t>
+    <t>Ms. Jacinda Perez returned the P1,500.00 to Ms. Fortin during the audit.</t>
   </si>
   <si>
     <t>Follow-up with HR</t>
